--- a/data/gravel/Pivot Vault 2025.xlsx
+++ b/data/gravel/Pivot Vault 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98E17BE-2135-4148-BA0F-4DEA17A53212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ACB5DC-97A9-9C44-B749-9802A750DE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23820" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -1382,9 +1382,6 @@
       <c r="A44" t="s">
         <v>70</v>
       </c>
-      <c r="B44" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">

--- a/data/gravel/Pivot Vault 2025.xlsx
+++ b/data/gravel/Pivot Vault 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ACB5DC-97A9-9C44-B749-9802A750DE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9F23FE-48C2-2244-A550-D4DA02B45031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23820" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32520" yWindow="-18020" windowWidth="23820" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://portal.pivotcycles.com/portalimages/bikes/clv/00VLTV670CXPE1-GMMMDSTDHN.png</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Pivot Vault 2025.xlsx
+++ b/data/gravel/Pivot Vault 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9F23FE-48C2-2244-A550-D4DA02B45031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F2E99A-A376-3D4D-8084-1036A58D2A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32520" yWindow="-18020" windowWidth="23820" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -356,17 +356,32 @@
   </si>
   <si>
     <t>https://portal.pivotcycles.com/portalimages/bikes/clv/00VLTV670CXPE1-GMMMDSTDHN.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Tempe, Arizona, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -389,8 +404,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1577,6 +1593,17 @@
       <c r="A73" t="s">
         <v>104</v>
       </c>
+      <c r="B73" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" t="s">
+        <v>113</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Pivot Vault 2025.xlsx
+++ b/data/gravel/Pivot Vault 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F2E99A-A376-3D4D-8084-1036A58D2A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462CECB8-B638-3E46-91CE-C4348831552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -365,6 +365,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -703,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1434,174 +1452,204 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>86</v>
-      </c>
-      <c r="B57" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>81</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>89</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>93</v>
-      </c>
-      <c r="B64" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>94</v>
-      </c>
-      <c r="B65" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>96</v>
-      </c>
-      <c r="B67" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>91</v>
+      </c>
+      <c r="B68" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>95</v>
+      </c>
+      <c r="B72" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>104</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
+      </c>
+      <c r="B73" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>101</v>
+      </c>
+      <c r="B77" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>112</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>113</v>
       </c>
     </row>

--- a/data/gravel/Pivot Vault 2025.xlsx
+++ b/data/gravel/Pivot Vault 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462CECB8-B638-3E46-91CE-C4348831552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CC41EC-9E64-1444-8315-A30F8FD8F5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5600" yWindow="760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
